--- a/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
@@ -4043,7 +4043,7 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>dwg_revision</t>
+          <t>dwg_supersedure, dwg_revision</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>dwg_file, sys_approval_request</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>sys_role_permission</t>
+          <t>doc_control, sys_role_permission</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>prt_part, com_company</t>
+          <t>prt_supplier_code_map</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>erp_warehouse, mat_material</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
@@ -2393,7 +2393,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>code_relationship</t>
+          <t>code_relationship, code_relationship_slot_map</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="J169" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_tenant</t>
         </is>
       </c>
       <c r="K169" s="5" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커버리지" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추적표'!$A$1:$K$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추적표'!$A$1:$L$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:L180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,7 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,6 +642,11 @@
           <t>Phase</t>
         </is>
       </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>작업자</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
@@ -696,6 +702,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -751,6 +762,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -806,6 +822,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -861,6 +882,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -916,6 +942,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -971,6 +1002,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -1026,6 +1062,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1081,6 +1122,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -1136,6 +1182,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1191,6 +1242,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -1246,6 +1302,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1301,6 +1362,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -1356,6 +1422,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1411,6 +1482,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -1466,6 +1542,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1521,6 +1602,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -1576,6 +1662,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1631,6 +1722,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1686,6 +1782,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1741,6 +1842,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1796,6 +1902,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1851,6 +1962,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1906,6 +2022,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1961,6 +2082,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -2016,6 +2142,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -2071,6 +2202,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -2126,6 +2262,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -2181,6 +2322,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -2236,6 +2382,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -2291,6 +2442,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -2346,6 +2502,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -2401,6 +2562,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -2456,6 +2622,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2511,6 +2682,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -2566,6 +2742,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -2621,6 +2802,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -2676,6 +2862,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -2731,6 +2922,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -2786,6 +2982,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2841,6 +3042,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -2896,6 +3102,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -2951,6 +3162,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -3006,6 +3222,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -3061,6 +3282,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -3116,6 +3342,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -3171,6 +3402,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -3226,6 +3462,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -3281,6 +3522,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -3336,6 +3582,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -3391,6 +3642,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -3446,6 +3702,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -3501,6 +3762,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -3556,6 +3822,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -3611,6 +3882,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -3666,6 +3942,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -3721,6 +4002,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -3776,6 +4062,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -3831,6 +4122,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -3886,6 +4182,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -3941,6 +4242,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -3996,6 +4302,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -4051,6 +4362,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -4106,6 +4422,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -4161,6 +4482,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -4216,6 +4542,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -4271,6 +4602,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -4326,6 +4662,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -4381,6 +4722,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -4436,6 +4782,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -4491,6 +4842,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -4546,6 +4902,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -4601,6 +4962,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -4656,6 +5022,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -4711,6 +5082,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -4766,6 +5142,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -4821,6 +5202,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -4876,6 +5262,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -4931,6 +5322,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -4986,6 +5382,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -5041,6 +5442,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -5096,6 +5502,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -5151,6 +5562,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -5206,6 +5622,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -5261,6 +5682,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
@@ -5316,6 +5742,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -5371,6 +5802,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
@@ -5426,6 +5862,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -5481,6 +5922,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
@@ -5536,6 +5982,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -5591,6 +6042,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
@@ -5646,6 +6102,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -5701,6 +6162,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -5756,6 +6222,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -5811,6 +6282,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
@@ -5866,6 +6342,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -5921,6 +6402,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -5976,6 +6462,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -6031,6 +6522,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
@@ -6086,6 +6582,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -6141,6 +6642,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
@@ -6196,6 +6702,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -6251,6 +6762,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -6306,6 +6822,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -6361,6 +6882,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
@@ -6416,6 +6942,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
@@ -6471,6 +7002,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
@@ -6526,6 +7062,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -6581,6 +7122,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
@@ -6636,6 +7182,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
@@ -6691,6 +7242,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
@@ -6746,6 +7302,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -6801,6 +7362,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
@@ -6856,6 +7422,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -6911,6 +7482,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
@@ -6966,6 +7542,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
@@ -7021,6 +7602,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
@@ -7076,6 +7662,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
@@ -7131,6 +7722,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
@@ -7186,6 +7782,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
@@ -7241,6 +7842,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
@@ -7296,6 +7902,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
@@ -7351,6 +7962,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
@@ -7406,6 +8022,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
@@ -7461,6 +8082,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
@@ -7516,6 +8142,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
@@ -7571,6 +8202,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
@@ -7626,6 +8262,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
@@ -7681,6 +8322,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
@@ -7736,6 +8382,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
@@ -7791,6 +8442,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
@@ -7846,6 +8502,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
@@ -7901,6 +8562,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
@@ -7956,6 +8622,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
@@ -8011,6 +8682,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
@@ -8066,6 +8742,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
@@ -8121,6 +8802,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
@@ -8176,6 +8862,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
@@ -8231,6 +8922,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
@@ -8286,6 +8982,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
@@ -8341,6 +9042,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
@@ -8396,6 +9102,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
@@ -8451,6 +9162,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
@@ -8506,6 +9222,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
@@ -8561,6 +9282,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
@@ -8616,6 +9342,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
@@ -8671,6 +9402,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
@@ -8726,6 +9462,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
@@ -8781,6 +9522,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
@@ -8836,6 +9582,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
@@ -8891,6 +9642,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
@@ -8946,6 +9702,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
@@ -9001,6 +9762,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
@@ -9056,6 +9822,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
@@ -9111,6 +9882,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
@@ -9166,6 +9942,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
@@ -9221,6 +10002,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
@@ -9276,6 +10062,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
@@ -9331,6 +10122,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
@@ -9386,6 +10182,11 @@
           <t>P4</t>
         </is>
       </c>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
@@ -9441,6 +10242,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
@@ -9496,6 +10302,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L162" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
@@ -9551,6 +10362,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L163" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
@@ -9606,6 +10422,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L164" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
@@ -9661,6 +10482,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L165" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
@@ -9716,6 +10542,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L166" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
@@ -9771,6 +10602,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L167" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
@@ -9826,6 +10662,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L168" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
@@ -9881,6 +10722,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L169" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
@@ -9936,6 +10782,11 @@
           <t>P1</t>
         </is>
       </c>
+      <c r="L170" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
@@ -9991,6 +10842,11 @@
           <t>P2</t>
         </is>
       </c>
+      <c r="L171" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
@@ -10046,6 +10902,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L172" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n">
@@ -10101,6 +10962,11 @@
           <t>P3</t>
         </is>
       </c>
+      <c r="L173" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
@@ -10156,6 +11022,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L174" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
@@ -10211,6 +11082,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L175" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
@@ -10266,6 +11142,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L176" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
@@ -10321,6 +11202,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n">
@@ -10376,6 +11262,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L178" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
@@ -10431,6 +11322,11 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
@@ -10486,9 +11382,14 @@
           <t>P5</t>
         </is>
       </c>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K180"/>
+  <autoFilter ref="A1:L180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-23</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-23</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-23</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-23 · W-24</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-22</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-20</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-20</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-20</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-20</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-20</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-20</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-17</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>W-08</t>
+          <t>W-08 · W-18</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-24</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-21</t>
         </is>
       </c>
       <c r="I131" s="7" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-19</t>
         </is>
       </c>
       <c r="I140" s="7" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-19</t>
         </is>
       </c>
       <c r="I145" s="7" t="inlineStr">

--- a/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커버리지" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추적표'!$A$1:$L$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'추적표'!$A$1:$L$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -542,7 +542,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>179건 (요구사항 50 × 기능 매핑)</t>
+          <t>180건 (요구사항 50 × 기능 매핑)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>기능 178/178 연결 · 미연결 0건 · 해석불가 0건 (커버리지 시트 참조)</t>
+          <t>기능 179/179 연결 · 미연결 0건 · 해석불가 0건 (커버리지 시트 참조)</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1852,54 +1852,54 @@
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-007</t>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-006</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Sub Code 등록</t>
+          <t>Main Work Frame</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>CODE-001</t>
+          <t>SYS-021</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>코드 그룹 등록</t>
+          <t>다국어 지원 (i18n)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>CODE RCCS 코드 관리</t>
+          <t>SYS 시스템 공통</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>M-3-1</t>
+          <t>M-14-11 · M-15-7</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>W-04</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>SVC-03, FE-02</t>
+          <t>FE-01, SVC-01</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>code_group</t>
+          <t>sys_translation, sys_user</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1912,7 +1912,7 @@
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>REQ-F-007</t>
         </is>
@@ -1924,12 +1924,12 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>CODE-002</t>
+          <t>CODE-001</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>코드 자릿수 정의</t>
+          <t>코드 그룹 등록</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>SVC-03</t>
+          <t>SVC-03, FE-02</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>code_item</t>
+          <t>code_group</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>CODE-003</t>
+          <t>CODE-002</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>자릿수 값 등록</t>
+          <t>코드 자릿수 정의</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>code_item_value</t>
+          <t>code_item</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>CODE-004</t>
+          <t>CODE-003</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Table 참조 값 연결</t>
+          <t>자릿수 값 등록</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>SVC-03, SVC-05</t>
+          <t>SVC-03</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>CODE-005</t>
+          <t>CODE-004</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>자재·일반구매품 코드 등록</t>
+          <t>Table 참조 값 연결</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>M-3-2</t>
+          <t>M-3-1</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SVC-03</t>
+          <t>SVC-03, SVC-05</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>code_group, code_item_value</t>
+          <t>code_item_value</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>CODE-013</t>
+          <t>CODE-005</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>코드 승인</t>
+          <t>자재·일반구매품 코드 등록</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2179,22 +2179,22 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-3-2</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-04</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>SVC-03</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>code_*</t>
+          <t>code_group, code_item_value</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>CODE-014</t>
+          <t>CODE-013</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>등록 Code Table 조회</t>
+          <t>코드 승인</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>SVC-03, FE-02</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>CODE-015</t>
+          <t>CODE-014</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>코드 자산 연결</t>
+          <t>등록 Code Table 조회</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2299,22 +2299,22 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>M-3-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>W-04</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>SVC-03, SVC-04, SVC-05</t>
+          <t>SVC-03, FE-02</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>product_code, dwg_file, tbl_data_table</t>
+          <t>code_*</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CODE-016</t>
+          <t>CODE-015</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>코드 Excel Import/Export</t>
+          <t>코드 자산 연결</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2359,27 +2359,27 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-3-1</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-04</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>SVC-03, INT-03</t>
+          <t>SVC-03, SVC-04, SVC-05</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>code_item_value</t>
+          <t>product_code, dwg_file, tbl_data_table</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2392,24 +2392,24 @@
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-008</t>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-007</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Product Code 관리</t>
+          <t>Sub Code 등록</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>CODE-006</t>
+          <t>CODE-016</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Product Code 등록</t>
+          <t>코드 Excel Import/Export</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2419,27 +2419,27 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>M-3-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>W-04</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>SVC-03</t>
+          <t>SVC-03, INT-03</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>product_code</t>
+          <t>code_item_value</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2452,7 +2452,7 @@
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>REQ-F-008</t>
         </is>
@@ -2464,12 +2464,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>CODE-007</t>
+          <t>CODE-006</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Product Code 자릿수 구성</t>
+          <t>Product Code 등록</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>product_code_item</t>
+          <t>product_code</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2512,24 +2512,24 @@
       <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-009</t>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-008</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Code Relationship</t>
+          <t>Product Code 관리</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>CODE-008</t>
+          <t>CODE-007</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Code Relationship 설정</t>
+          <t>Product Code 자릿수 구성</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>M-3-4</t>
+          <t>M-3-3</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>W-05</t>
+          <t>W-04</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>code_relationship, code_relationship_slot_map</t>
+          <t>product_code_item</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2572,7 +2572,7 @@
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>REQ-F-009</t>
         </is>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>CODE-009</t>
+          <t>CODE-008</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Part List Running Test</t>
+          <t>Code Relationship 설정</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>code_relationship</t>
+          <t>code_relationship, code_relationship_slot_map</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2632,24 +2632,24 @@
       <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-010</t>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-009</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>BOM 자동 전개</t>
+          <t>Code Relationship</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>CODE-010</t>
+          <t>CODE-009</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>BOM 전개</t>
+          <t>Part List Running Test</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>SVC-03, ENG-02</t>
+          <t>SVC-03</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>code_relationship, cpq_selection_item</t>
+          <t>code_relationship</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2694,22 +2694,22 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-011</t>
+          <t>REQ-F-010</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Arrangement</t>
+          <t>BOM 자동 전개</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>CODE-011</t>
+          <t>CODE-010</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Arrangement Code 등록</t>
+          <t>BOM 전개</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2719,27 +2719,27 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>M-3-5</t>
+          <t>M-3-4</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>W-04</t>
+          <t>W-05</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>SVC-03</t>
+          <t>SVC-03, ENG-02</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>arrangement_code</t>
+          <t>code_relationship, cpq_selection_item</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2752,7 +2752,7 @@
       <c r="A37" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>REQ-F-011</t>
         </is>
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>CODE-012</t>
+          <t>CODE-011</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Arrangement 구성 설정</t>
+          <t>Arrangement Code 등록</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2779,22 +2779,22 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>M-3-6</t>
+          <t>M-3-5</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>W-06</t>
+          <t>W-04</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>SVC-03, SVC-04</t>
+          <t>SVC-03</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>arrangement_component</t>
+          <t>arrangement_code</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2812,34 +2812,34 @@
       <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-012</t>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-011</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>도면 관리</t>
+          <t>Arrangement</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>DWG-001</t>
+          <t>CODE-012</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>도면 등록</t>
+          <t>Arrangement 구성 설정</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>DWG 도면·PLM</t>
+          <t>CODE RCCS 코드 관리</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>M-4-1</t>
+          <t>M-3-6</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-03, SVC-04</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>dwg_drawing</t>
+          <t>arrangement_component</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2872,7 +2872,7 @@
       <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>REQ-F-012</t>
         </is>
@@ -2884,12 +2884,12 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>DWG-013</t>
+          <t>DWG-001</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>도면 개정 관리</t>
+          <t>도면 등록</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>dwg_revision</t>
+          <t>dwg_drawing</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>DWG-014</t>
+          <t>DWG-013</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>도면 승인</t>
+          <t>도면 개정 관리</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, SVC-10</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>dwg_approval</t>
+          <t>dwg_revision</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -2992,24 +2992,24 @@
       <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-013</t>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-012</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Drawing Editor</t>
+          <t>도면 관리</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DWG-002</t>
+          <t>DWG-014</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>부품 호출·배치</t>
+          <t>도면 승인</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>FE-02, SVC-04</t>
+          <t>SVC-04, SVC-10</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_approval</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>REQ-F-013</t>
         </is>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DWG-003</t>
+          <t>DWG-002</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>CAD 편집 명령</t>
+          <t>부품 호출·배치</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>FE-02</t>
+          <t>FE-02, SVC-04</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>DWG-004</t>
+          <t>DWG-003</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>선택·스냅</t>
+          <t>CAD 편집 명령</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>DWG-005</t>
+          <t>DWG-004</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>치수선·지시선</t>
+          <t>선택·스냅</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>FE-02, SVC-04</t>
+          <t>FE-02</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>dwg_dimension</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>DWG-012</t>
+          <t>DWG-005</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Block 저장·호출</t>
+          <t>치수선·지시선</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>FE-02, SVC-04</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_dimension</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>DWG-022</t>
+          <t>DWG-012</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>도면 Templet 관리</t>
+          <t>Block 저장·호출</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, SVC-06</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>DWG-025</t>
+          <t>DWG-022</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>측정·특성 도구</t>
+          <t>도면 Templet 관리</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>M-0-4 · M-4-1</t>
+          <t>M-4-1</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>FE-02</t>
+          <t>SVC-04, SVC-06</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -3412,24 +3412,24 @@
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-014</t>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-013</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>파라메트릭 치수</t>
+          <t>Drawing Editor</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>DWG-006</t>
+          <t>DWG-025</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>치수 Macro 바인딩</t>
+          <t>측정·특성 도구</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>M-4-1</t>
+          <t>M-0-4 · M-4-1</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-01</t>
+          <t>FE-02</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>dwg_dimension, tbx_macro</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -3472,7 +3472,7 @@
       <c r="A49" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>REQ-F-014</t>
         </is>
@@ -3484,12 +3484,12 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>DWG-007</t>
+          <t>DWG-006</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>치수·부품 동기화</t>
+          <t>치수 Macro 바인딩</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>FE-02, ENG-03</t>
+          <t>SVC-04, ENG-01</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_dimension, tbx_macro</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>DWG-008</t>
+          <t>DWG-007</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>설계·자료 우선순위</t>
+          <t>치수·부품 동기화</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-01</t>
+          <t>FE-02, ENG-03</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>dwg_dimension</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -3592,24 +3592,24 @@
       <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-015</t>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-014</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>부품 관계·검증</t>
+          <t>파라메트릭 치수</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>DWG-009</t>
+          <t>DWG-008</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>부품 상호관계 설정</t>
+          <t>설계·자료 우선순위</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-04, ENG-01</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>dwg_part_relation</t>
+          <t>dwg_dimension</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="A52" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>REQ-F-015</t>
         </is>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DWG-010</t>
+          <t>DWG-009</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>설계 검증 규칙</t>
+          <t>부품 상호관계 설정</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-01</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>dwg_verification</t>
+          <t>dwg_part_relation</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>DWG-011</t>
+          <t>DWG-010</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>조립 순서 Set-up</t>
+          <t>설계 검증 규칙</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-04, ENG-01</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>dwg_bom</t>
+          <t>dwg_verification</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DWG-024</t>
+          <t>DWG-011</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>설계 Simulation</t>
+          <t>조립 순서 Set-up</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -3809,17 +3809,17 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>FE-02, ENG-01</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>dwg_bom</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -3832,24 +3832,24 @@
       <c r="A55" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-016</t>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-015</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>도면 Import/Export</t>
+          <t>부품 관계·검증</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>DWG-015</t>
+          <t>DWG-024</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>도면 Import</t>
+          <t>설계 Simulation</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, INT-04</t>
+          <t>FE-02, ENG-01</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>dwg_file, dwg_document</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -3892,7 +3892,7 @@
       <c r="A56" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>REQ-F-016</t>
         </is>
@@ -3904,12 +3904,12 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DWG-016</t>
+          <t>DWG-015</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>도면 Export</t>
+          <t>도면 Import</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, ENG-03</t>
+          <t>SVC-04, INT-04</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>dwg_file, dwg_document</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>DWG-023</t>
+          <t>DWG-016</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>CAD Mapping</t>
+          <t>도면 Export</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -3989,17 +3989,17 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, INT-04</t>
+          <t>SVC-04, ENG-03</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>dwg_file</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -4012,24 +4012,24 @@
       <c r="A58" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-017</t>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-016</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>부품·재질·PLM 조회</t>
+          <t>도면 Import/Export</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>DWG-017</t>
+          <t>DWG-023</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>부품 마스터</t>
+          <t>CAD Mapping</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -4039,27 +4039,27 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-4-1</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-06</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-04, INT-04</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>prt_part</t>
+          <t>dwg_file</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
@@ -4072,7 +4072,7 @@
       <c r="A59" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>REQ-F-017</t>
         </is>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>DWG-018</t>
+          <t>DWG-017</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>재질 마스터</t>
+          <t>부품 마스터</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>mat_material</t>
+          <t>prt_part</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DWG-019</t>
+          <t>DWG-018</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>도면 BOM 관리</t>
+          <t>재질 마스터</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>dwg_bom</t>
+          <t>mat_material</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>DWG-020</t>
+          <t>DWG-019</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>첨부파일 관리</t>
+          <t>도면 BOM 관리</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>SVC-04, SVC-12</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>dwg_file</t>
+          <t>dwg_bom</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DWG-026</t>
+          <t>DWG-020</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Referencers 역참조 조회</t>
+          <t>첨부파일 관리</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -4279,27 +4279,27 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>M-4-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>W-06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>SVC-04, SVC-12</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>dwg_bom, code_relationship</t>
+          <t>dwg_file</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>DWG-027</t>
+          <t>DWG-026</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Variants·Supersedure 관리</t>
+          <t>Referencers 역참조 조회</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>dwg_supersedure, dwg_revision</t>
+          <t>dwg_bom, code_relationship</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -4372,54 +4372,54 @@
       <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-018</t>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-017</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>데이터 Table 관리</t>
+          <t>부품·재질·PLM 조회</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>TBL-001</t>
+          <t>DWG-027</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Table 정의</t>
+          <t>Variants·Supersedure 관리</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>TBL 데이터 Table</t>
+          <t>DWG 도면·PLM</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>M-3-7</t>
+          <t>M-4-1</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>W-20</t>
+          <t>W-06</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>SVC-05</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>dwg_supersedure, dwg_revision</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -4432,7 +4432,7 @@
       <c r="A65" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>REQ-F-018</t>
         </is>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>TBL-002</t>
+          <t>TBL-001</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Table 행 편집</t>
+          <t>Table 정의</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>tbl_data_row</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>TBL-003</t>
+          <t>TBL-002</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Excel Import</t>
+          <t>Table 행 편집</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>SVC-05, INT-03</t>
+          <t>SVC-05</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>TBL-004</t>
+          <t>TBL-003</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Table 범위 조회</t>
+          <t>Excel Import</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>SVC-05, ENG-01</t>
+          <t>SVC-05, INT-03</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>TBL-005</t>
+          <t>TBL-004</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Data Up-Load</t>
+          <t>Table 범위 조회</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -4649,17 +4649,17 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>SVC-05, SVC-12</t>
+          <t>SVC-05, ENG-01</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>tbl_data_table, dwg_file</t>
+          <t>tbl_data_row</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>TBL-006</t>
+          <t>TBL-005</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Table 승인</t>
+          <t>Data Up-Load</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -4709,17 +4709,17 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>SVC-05, SVC-12</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>tbl_data_table, dwg_file</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
@@ -4732,54 +4732,54 @@
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-019</t>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-018</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>데이터 Table 관리</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>TBX-001</t>
+          <t>TBL-006</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>UI Designer 위젯 배치</t>
+          <t>Table 승인</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>TBX Toolbox</t>
+          <t>TBL 데이터 Table</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>M-1-1 · M-1-2</t>
+          <t>M-3-7</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>W-08</t>
+          <t>W-20</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>FE-03, SVC-06</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -4792,7 +4792,7 @@
       <c r="A71" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>REQ-F-019</t>
         </is>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>TBX-002</t>
+          <t>TBX-001</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>동작 Templet 바인딩</t>
+          <t>UI Designer 위젯 배치</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>tbx_ui_form, tbx_templet</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>TBX-003</t>
+          <t>TBX-002</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Form 저장·버전·게시</t>
+          <t>동작 Templet 바인딩</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>M-1-1 · M-1-2 · M-14-9</t>
+          <t>M-1-1 · M-1-2</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>SVC-06, SVC-10</t>
+          <t>FE-03, SVC-06</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbx_ui_form, tbx_templet</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>TBX-004</t>
+          <t>TBX-003</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>AI UI 제안</t>
+          <t>Form 저장·버전·게시</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>M-1-1 · M-1-2</t>
+          <t>M-1-1 · M-1-2 · M-14-9</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>AI-04, FE-03</t>
+          <t>SVC-06, SVC-10</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>TBX-013</t>
+          <t>TBX-004</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Templet 관리</t>
+          <t>AI UI 제안</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -4999,22 +4999,22 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>M-0-6 · M-1-6</t>
+          <t>M-1-1 · M-1-2</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>W-07</t>
+          <t>W-08</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>SVC-06</t>
+          <t>AI-04, FE-03</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -5032,24 +5032,24 @@
       <c r="A75" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-020</t>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-019</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Macro 엔진</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>TBX-006</t>
+          <t>TBX-013</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Macro 수식 편집</t>
+          <t>Templet 관리</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>M-1-7</t>
+          <t>M-0-6 · M-1-6</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -5069,17 +5069,17 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>FE-03, ENG-01</t>
+          <t>SVC-06</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
@@ -5092,7 +5092,7 @@
       <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>REQ-F-020</t>
         </is>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>TBX-011</t>
+          <t>TBX-006</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Macro Test Run</t>
+          <t>Macro 수식 편집</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>ENG-01</t>
+          <t>FE-03, ENG-01</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>TBX-012</t>
+          <t>TBX-011</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Macro 승인·버전</t>
+          <t>Macro Test Run</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>ENG-01</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
@@ -5212,24 +5212,24 @@
       <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-021</t>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-020</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>4-Way Sync</t>
+          <t>Macro 엔진</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>TBX-005</t>
+          <t>TBX-012</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Prompt 입력</t>
+          <t>Macro 승인·버전</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>FE-03, AI-03</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L78" s="5" t="inlineStr">
@@ -5272,7 +5272,7 @@
       <c r="A79" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>REQ-F-021</t>
         </is>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>TBX-007</t>
+          <t>TBX-005</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Flowchart 편집</t>
+          <t>Prompt 입력</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>FE-03</t>
+          <t>FE-03, AI-03</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>TBX-008</t>
+          <t>TBX-007</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>4-Way Sync 변환</t>
+          <t>Flowchart 편집</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>AI-03, ENG-01</t>
+          <t>FE-03</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
@@ -5392,24 +5392,24 @@
       <c r="A81" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-022</t>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-021</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>지원 도구</t>
+          <t>4-Way Sync</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>TBX-009</t>
+          <t>TBX-008</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>함수·그래프 마법사</t>
+          <t>4-Way Sync 변환</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>FE-03</t>
+          <t>AI-03, ENG-01</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
@@ -5452,7 +5452,7 @@
       <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>REQ-F-022</t>
         </is>
@@ -5464,12 +5464,12 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>TBX-010</t>
+          <t>TBX-009</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Data Information Call</t>
+          <t>함수·그래프 마법사</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>FE-03, SVC-05</t>
+          <t>FE-03</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>TBX-014</t>
+          <t>TBX-010</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>기능 찾기·도움말</t>
+          <t>Data Information Call</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -5539,22 +5539,22 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-1-7</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-07</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>AI-03, FE-03</t>
+          <t>FE-03, SVC-05</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>TBX-015</t>
+          <t>TBX-014</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>인터넷 검색·AI 질의</t>
+          <t>기능 찾기·도움말</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>M-1-8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>AI-05, FE-03</t>
+          <t>AI-03, FE-03</t>
         </is>
       </c>
       <c r="J84" s="7" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L84" s="5" t="inlineStr">
@@ -5632,54 +5632,54 @@
       <c r="A85" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-023</t>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-022</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>제품 선정</t>
+          <t>지원 도구</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>CPQ-001</t>
+          <t>TBX-015</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>제품 선정 화면</t>
+          <t>인터넷 검색·AI 질의</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>CPQ CPQ 제품선정</t>
+          <t>TBX Toolbox</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>M-5-1</t>
+          <t>M-1-8</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>W-02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>FE-01, SVC-07</t>
+          <t>AI-05, FE-03</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L85" s="5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>REQ-F-023</t>
         </is>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>CPQ-002</t>
+          <t>CPQ-001</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Arrangement 구성</t>
+          <t>제품 선정 화면</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection, arrangement_*</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>CPQ-003</t>
+          <t>CPQ-002</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>사양 입력</t>
+          <t>Arrangement 구성</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>cpq_selection, arrangement_*</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>CPQ-010</t>
+          <t>CPQ-003</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>DWG View</t>
+          <t>사양 입력</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>FE-01</t>
+          <t>FE-01, SVC-07</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
@@ -5872,24 +5872,24 @@
       <c r="A89" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-024</t>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-023</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>사양 Excel Import</t>
+          <t>제품 선정</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>CPQ-004</t>
+          <t>CPQ-010</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>고객 사양 Excel Import</t>
+          <t>DWG View</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>INT-03, SVC-07</t>
+          <t>FE-01</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L89" s="5" t="inlineStr">
@@ -5934,22 +5934,22 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-025</t>
+          <t>REQ-F-024</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>기술 데이터·Document</t>
+          <t>사양 Excel Import</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>CPQ-005</t>
+          <t>CPQ-004</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>기술 데이터 화면</t>
+          <t>고객 사양 Excel Import</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -5959,22 +5959,22 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>M-5-2</t>
+          <t>M-5-1</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>W-03</t>
+          <t>W-02</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>FE-01, SVC-07</t>
+          <t>INT-03, SVC-07</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection, tbl_*</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
@@ -5992,7 +5992,7 @@
       <c r="A91" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>REQ-F-025</t>
         </is>
@@ -6004,12 +6004,12 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>CPQ-006</t>
+          <t>CPQ-005</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Document Template</t>
+          <t>기술 데이터 화면</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -6019,22 +6019,22 @@
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>M-5-3</t>
+          <t>M-5-2</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>W-17</t>
+          <t>W-03</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>FE-01, ENG-01</t>
+          <t>FE-01, SVC-07</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>cpq_selection, tbl_*</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
@@ -6052,24 +6052,24 @@
       <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-026</t>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-025</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>완성품 Code·X-Code</t>
+          <t>기술 데이터·Document</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>CPQ-007</t>
+          <t>CPQ-006</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>완성품 Code 생성</t>
+          <t>Document Template</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -6079,27 +6079,27 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>M-5-1</t>
+          <t>M-5-3</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>W-02</t>
+          <t>W-17</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>SVC-07, SVC-03</t>
+          <t>FE-01, ENG-01</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L92" s="5" t="inlineStr">
@@ -6112,7 +6112,7 @@
       <c r="A93" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>REQ-F-026</t>
         </is>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>CPQ-008</t>
+          <t>CPQ-007</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Sub Item List 조회</t>
+          <t>완성품 Code 생성</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>SVC-07</t>
+          <t>SVC-07, SVC-03</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection_item</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>CPQ-009</t>
+          <t>CPQ-008</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>X-Code 비규격 처리</t>
+          <t>Sub Item List 조회</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection</t>
+          <t>cpq_selection_item</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
@@ -6232,24 +6232,24 @@
       <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-027</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-026</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>CPQ Set-up</t>
+          <t>완성품 Code·X-Code</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>CPQ-011</t>
+          <t>CPQ-009</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Selection Set-up</t>
+          <t>X-Code 비규격 처리</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -6259,22 +6259,22 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>M-2-1</t>
+          <t>M-5-1</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-02</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>FE-02, SVC-06</t>
+          <t>SVC-07</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>cpq_selection</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
@@ -6292,7 +6292,7 @@
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>REQ-F-027</t>
         </is>
@@ -6304,12 +6304,12 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>CPQ-012</t>
+          <t>CPQ-011</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Technical·Document Set-up</t>
+          <t>Selection Set-up</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>M-2-2 · M-2-3</t>
+          <t>M-2-1</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>CPQ-013</t>
+          <t>CPQ-012</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Print Set-up</t>
+          <t>Technical·Document Set-up</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -6379,17 +6379,17 @@
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>M-1-3 · M-2-4</t>
+          <t>M-2-2 · M-2-3</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>W-08 · W-18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>FE-02, SVC-11</t>
+          <t>FE-02, SVC-06</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>CPQ-014</t>
+          <t>CPQ-013</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Selection Toolbar 구성</t>
+          <t>Print Set-up</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>M-0-4 · M-1-5</t>
+          <t>M-1-3 · M-2-4</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>W-08</t>
+          <t>W-08 · W-18</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>FE-02, SVC-06</t>
+          <t>FE-02, SVC-11</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>CPQ-015</t>
+          <t>CPQ-014</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>Module 이미지 제작</t>
+          <t>Selection Toolbar 구성</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -6499,22 +6499,22 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-0-4 · M-1-5</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-08</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>FE-02, SVC-04</t>
+          <t>FE-02, SVC-06</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
@@ -6532,29 +6532,29 @@
       <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-028</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-027</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>일괄 자동 생성</t>
+          <t>CPQ Set-up</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>RUN-001</t>
+          <t>CPQ-015</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Run 실행 요청</t>
+          <t>Module 이미지 제작</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>RUN EDIM Run</t>
+          <t>CPQ CPQ 제품선정</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -6569,17 +6569,17 @@
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>SVC-07, ENG-02</t>
+          <t>FE-02, SVC-04</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>cpq_run</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L100" s="5" t="inlineStr">
@@ -6592,7 +6592,7 @@
       <c r="A101" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>REQ-F-028</t>
         </is>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>RUN-002</t>
+          <t>RUN-001</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>BOM·Part List 생성</t>
+          <t>Run 실행 요청</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>M-7-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>ENG-02, SVC-03</t>
+          <t>SVC-07, ENG-02</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>cpq_selection_item, cpq_output</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>RUN-003</t>
+          <t>RUN-002</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>치수 Macro 일괄 실행</t>
+          <t>BOM·Part List 생성</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>M-7-3</t>
+          <t>M-7-2</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>ENG-02, ENG-01</t>
+          <t>ENG-02, SVC-03</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>cpq_run.dimension_values</t>
+          <t>cpq_selection_item, cpq_output</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>RUN-004</t>
+          <t>RUN-003</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>승인도면 생성</t>
+          <t>치수 Macro 일괄 실행</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>ENG-03</t>
+          <t>ENG-02, ENG-01</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>cpq_output, dwg_file</t>
+          <t>cpq_run.dimension_values</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>RUN-005</t>
+          <t>RUN-004</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>제작도면 생성</t>
+          <t>승인도면 생성</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>cpq_output</t>
+          <t>cpq_output, dwg_file</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>RUN-006</t>
+          <t>RUN-005</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>기술자료 계산·생성</t>
+          <t>제작도면 생성</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-7-3</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>ENG-02, ENG-01</t>
+          <t>ENG-03</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>RUN-007</t>
+          <t>RUN-006</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>일반 서류 생성</t>
+          <t>기술자료 계산·생성</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>ENG-02, SVC-11</t>
+          <t>ENG-02, ENG-01</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
@@ -6952,24 +6952,24 @@
       <c r="A107" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-029</t>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-028</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Run 모니터링·산출물</t>
+          <t>일괄 자동 생성</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>RUN-008</t>
+          <t>RUN-007</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Run 상태·오류 조회</t>
+          <t>일반 서류 생성</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
@@ -6989,17 +6989,17 @@
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>SVC-07</t>
+          <t>ENG-02, SVC-11</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>cpq_run</t>
+          <t>cpq_output</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
@@ -7012,7 +7012,7 @@
       <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>REQ-F-029</t>
         </is>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>RUN-009</t>
+          <t>RUN-008</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>산출물 조회</t>
+          <t>Run 상태·오류 조회</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -7039,22 +7039,22 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>M-15-8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>W-24</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>SVC-12</t>
+          <t>SVC-07</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>cpq_output, dwg_file</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -7072,24 +7072,24 @@
       <c r="A109" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-030</t>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-029</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>부분 Run·Export</t>
+          <t>Run 모니터링·산출물</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>RUN-010</t>
+          <t>RUN-009</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>BOM Export·부분 Run</t>
+          <t>산출물 조회</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
@@ -7099,22 +7099,22 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>M-7-2</t>
+          <t>M-15-8</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-24</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
-          <t>ENG-02, INT-03</t>
+          <t>SVC-12</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>cpq_run</t>
+          <t>cpq_output, dwg_file</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
@@ -7134,52 +7134,52 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-031</t>
+          <t>REQ-F-030</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>단가 관리</t>
+          <t>부분 Run·Export</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>CST-001</t>
+          <t>RUN-010</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>단가 관리</t>
+          <t>BOM Export·부분 Run</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>CST 원가·견적</t>
+          <t>RUN EDIM Run</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>M-12-5</t>
+          <t>M-7-2</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>W-13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>ENG-02, INT-03</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>cst_price</t>
+          <t>cpq_run</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
@@ -7192,7 +7192,7 @@
       <c r="A111" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>REQ-F-031</t>
         </is>
@@ -7204,22 +7204,22 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>ERP-021</t>
+          <t>CST-001</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>재고 단가 관리</t>
+          <t>단가 관리</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>ERP ERP 업무</t>
+          <t>CST 원가·견적</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>M-12-5 · M-8-4</t>
+          <t>M-12-5</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
@@ -7252,54 +7252,54 @@
       <c r="A112" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-032</t>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-031</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>원가 계산</t>
+          <t>단가 관리</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>CST-002</t>
+          <t>ERP-021</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>자재비 계산</t>
+          <t>재고 단가 관리</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>CST 원가·견적</t>
+          <t>ERP ERP 업무</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-12-5 · M-8-4</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-13</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>SVC-08, ENG-02</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>cst_calc</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
@@ -7312,7 +7312,7 @@
       <c r="A113" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>REQ-F-032</t>
         </is>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>CST-003</t>
+          <t>CST-002</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>제조비 계산</t>
+          <t>자재비 계산</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>SVC-08, ENG-02</t>
         </is>
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>cst_calc, erp_work_process</t>
+          <t>cst_calc</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
@@ -7384,12 +7384,12 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>CST-004</t>
+          <t>CST-003</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>직접비 집계</t>
+          <t>제조비 계산</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>cst_calc</t>
+          <t>cst_calc, erp_work_process</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -7444,17 +7444,17 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>ERP-028</t>
+          <t>CST-004</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>원가 DB 관리</t>
+          <t>직접비 집계</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>ERP ERP 업무</t>
+          <t>CST 원가·견적</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="J115" s="7" t="inlineStr">
         <is>
-          <t>cst_price</t>
+          <t>cst_calc</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr">
@@ -7492,34 +7492,34 @@
       <c r="A116" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-033</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-032</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>PCR·견적</t>
+          <t>원가 계산</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>CST-005</t>
+          <t>ERP-028</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>PCR 작성</t>
+          <t>원가 DB 관리</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>CST 원가·견적</t>
+          <t>ERP ERP 업무</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>M-14-5 · M-6-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -7529,17 +7529,17 @@
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>SVC-08, FE-01</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>cst_pcr</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
@@ -7552,7 +7552,7 @@
       <c r="A117" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>REQ-F-033</t>
         </is>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>CST-006</t>
+          <t>CST-005</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>견적서 생성·출력</t>
+          <t>PCR 작성</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>M-6-5</t>
+          <t>M-14-5 · M-6-4</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="I117" s="7" t="inlineStr">
         <is>
-          <t>SVC-08, SVC-11</t>
+          <t>SVC-08, FE-01</t>
         </is>
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>cst_quotation</t>
+          <t>cst_pcr</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>CST-007</t>
+          <t>CST-006</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>견적 이력 관리</t>
+          <t>견적서 생성·출력</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-6-5</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>SVC-08, SVC-11</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr">
@@ -7672,49 +7672,49 @@
       <c r="A119" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-034</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-033</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>문서 통제</t>
+          <t>PCR·견적</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>DOC-001</t>
+          <t>CST-007</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>문서 이력·Released Status</t>
+          <t>견적 이력 관리</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>DOC 문서 관리</t>
+          <t>CST 원가·견적</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>M-5-4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>W-11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>SVC-11, SVC-10</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>doc_control</t>
+          <t>cst_quotation</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
@@ -7732,7 +7732,7 @@
       <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>REQ-F-034</t>
         </is>
@@ -7744,12 +7744,12 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>DOC-002</t>
+          <t>DOC-001</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>관리 등급(보안 등급)</t>
+          <t>문서 이력·Released Status</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="I120" s="7" t="inlineStr">
         <is>
-          <t>SVC-01, SVC-11</t>
+          <t>SVC-11, SVC-10</t>
         </is>
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>doc_control, sys_role_permission</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>DOC-003</t>
+          <t>DOC-002</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Document Code 채번</t>
+          <t>관리 등급(보안 등급)</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>SVC-11</t>
+          <t>SVC-01, SVC-11</t>
         </is>
       </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>doc_control</t>
+          <t>doc_control, sys_role_permission</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>DOC-004</t>
+          <t>DOC-003</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>문서 보안 솔루션</t>
+          <t>Document Code 채번</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>M-14-10 · M-5-4</t>
+          <t>M-5-4</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>doc_control</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
@@ -7912,54 +7912,54 @@
       <c r="A123" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-035</t>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-034</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 관리</t>
+          <t>문서 통제</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>ERP-001</t>
+          <t>DOC-004</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 등록</t>
+          <t>문서 보안 솔루션</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>ERP ERP 업무</t>
+          <t>DOC 문서 관리</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>M-2-5 · M-6-2 · M-6-3</t>
+          <t>M-14-10 · M-5-4</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>W-09</t>
+          <t>W-11</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
-          <t>SVC-09, FE-01</t>
+          <t>SVC-11</t>
         </is>
       </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
-          <t>prj_project</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
@@ -7974,22 +7974,22 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-036</t>
+          <t>REQ-F-035</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>프로세스 상태기계</t>
+          <t>프로젝트 관리</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>ERP-002</t>
+          <t>ERP-001</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>프로세스 이벤트 관리</t>
+          <t>프로젝트 등록</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
@@ -7999,27 +7999,27 @@
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>M-14-7 · M-6-3</t>
+          <t>M-2-5 · M-6-2 · M-6-3</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>W-09 · W-14</t>
+          <t>W-09</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, FE-01</t>
         </is>
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>prj_project</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
@@ -8032,7 +8032,7 @@
       <c r="A125" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>REQ-F-036</t>
         </is>
@@ -8044,12 +8044,12 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>ERP-003</t>
+          <t>ERP-002</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>부서별 업무함</t>
+          <t>프로세스 이벤트 관리</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-14-7 · M-6-3</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-09 · W-14</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>SVC-09, FE-01</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J125" s="7" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>ERP-016</t>
+          <t>ERP-003</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>사용자 정의 ERP Toolbar</t>
+          <t>부서별 업무함</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -8119,22 +8119,22 @@
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>M-1-4 · M-14-9 · M-2-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>W-08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr">
         <is>
-          <t>SVC-06, FE-01</t>
+          <t>SVC-09, FE-01</t>
         </is>
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -8152,24 +8152,24 @@
       <c r="A127" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-037</t>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-036</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>영업 프로세스</t>
+          <t>프로세스 상태기계</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>ERP-004</t>
+          <t>ERP-016</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>영업 프로세스</t>
+          <t>사용자 정의 ERP Toolbar</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -8179,22 +8179,22 @@
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>M-6-4 · M-6-5 · M-6-6</t>
+          <t>M-1-4 · M-14-9 · M-2-5</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-08</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-06, FE-01</t>
         </is>
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       <c r="A128" s="5" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>REQ-F-037</t>
         </is>
@@ -8224,12 +8224,12 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>ERP-005</t>
+          <t>ERP-004</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>승인도서·고객승인</t>
+          <t>영업 프로세스</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>M-6-7</t>
+          <t>M-6-4 · M-6-5 · M-6-6</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>ERP-009</t>
+          <t>ERP-005</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>출고·납품 프로세스</t>
+          <t>승인도서·고객승인</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>M-6-8 · M-6-9</t>
+          <t>M-6-7</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>ERP-010</t>
+          <t>ERP-009</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>시운전·CS</t>
+          <t>출고·납품 프로세스</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>M-11-1 · M-6-10</t>
+          <t>M-6-8 · M-6-9</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -8392,24 +8392,24 @@
       <c r="A131" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-038</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-037</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>구매·자재</t>
+          <t>영업 프로세스</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>ERP-007</t>
+          <t>ERP-010</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>자재 프로세스</t>
+          <t>시운전·CS</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>M-8-2 · M-8-3</t>
+          <t>M-11-1 · M-6-10</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>W-21</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I131" s="7" t="inlineStr">
@@ -8452,7 +8452,7 @@
       <c r="A132" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>REQ-F-038</t>
         </is>
@@ -8464,12 +8464,12 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>ERP-017</t>
+          <t>ERP-007</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>구매 조건 관리</t>
+          <t>자재 프로세스</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>M-8-1 · M-8-6</t>
+          <t>M-8-2 · M-8-3</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-21</t>
         </is>
       </c>
       <c r="I132" s="7" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>com_company, erp_process_event</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>ERP-018</t>
+          <t>ERP-017</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>제품코드 매핑</t>
+          <t>구매 조건 관리</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>M-8-1</t>
+          <t>M-8-1 · M-8-6</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="I133" s="7" t="inlineStr">
         <is>
-          <t>SVC-09, SVC-03</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>prt_supplier_code_map</t>
+          <t>com_company, erp_process_event</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>ERP-019</t>
+          <t>ERP-018</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>재고 관리</t>
+          <t>제품코드 매핑</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>M-8-4</t>
+          <t>M-8-1</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="I134" s="7" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, SVC-03</t>
         </is>
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>erp_work_process</t>
+          <t>prt_supplier_code_map</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>ERP-020</t>
+          <t>ERP-019</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>창고 관리</t>
+          <t>재고 관리</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>erp_warehouse, mat_material</t>
+          <t>erp_work_process</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>ERP-021</t>
+          <t>ERP-020</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>재고 단가 관리</t>
+          <t>창고 관리</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
@@ -8719,22 +8719,22 @@
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>M-12-5 · M-8-4</t>
+          <t>M-8-4</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>W-13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="7" t="inlineStr">
         <is>
-          <t>SVC-08</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J136" s="7" t="inlineStr">
         <is>
-          <t>cst_price</t>
+          <t>erp_warehouse, mat_material</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>ERP-022</t>
+          <t>ERP-021</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>MRP 자재 소요 계획</t>
+          <t>재고 단가 관리</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
@@ -8779,22 +8779,22 @@
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>M-8-5</t>
+          <t>M-12-5 · M-8-4</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-13</t>
         </is>
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-08</t>
         </is>
       </c>
       <c r="J137" s="7" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>cst_price</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>ERP-026</t>
+          <t>ERP-022</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>자재흐름·물류 관리</t>
+          <t>MRP 자재 소요 계획</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-8-5</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="J138" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>ERP-029</t>
+          <t>ERP-026</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>불량·대체자재 관리</t>
+          <t>자재흐름·물류 관리</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>M-9-6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -8932,39 +8932,39 @@
       <c r="A140" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-039</t>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-038</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>구매·자재</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>DWG-021</t>
+          <t>ERP-029</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>Work Process 공정 데이터</t>
+          <t>불량·대체자재 관리</t>
         </is>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>DWG 도면·PLM</t>
+          <t>ERP ERP 업무</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>M-4-2</t>
+          <t>M-9-6</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>W-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I140" s="7" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="J140" s="7" t="inlineStr">
         <is>
-          <t>erp_work_process</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
@@ -8992,7 +8992,7 @@
       <c r="A141" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>REQ-F-039</t>
         </is>
@@ -9004,27 +9004,27 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>ERP-006</t>
+          <t>DWG-021</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>제작 프로세스</t>
+          <t>Work Process 공정 데이터</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>ERP ERP 업무</t>
+          <t>DWG 도면·PLM</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>M-7-1</t>
+          <t>M-4-2</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-19</t>
         </is>
       </c>
       <c r="I141" s="7" t="inlineStr">
@@ -9034,12 +9034,12 @@
       </c>
       <c r="J141" s="7" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>erp_work_process</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L141" s="5" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>ERP-008</t>
+          <t>ERP-006</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>생산 프로세스</t>
+          <t>제작 프로세스</t>
         </is>
       </c>
       <c r="F142" s="7" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>M-9-4</t>
+          <t>M-7-1</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -9124,12 +9124,12 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>ERP-023</t>
+          <t>ERP-008</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>생산 Scheduling·Capacity</t>
+          <t>생산 프로세스</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>M-9-1</t>
+          <t>M-9-4</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>ERP-024</t>
+          <t>ERP-023</t>
         </is>
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>작업지시 관리</t>
+          <t>생산 Scheduling·Capacity</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>M-9-2</t>
+          <t>M-9-1</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>SVC-09, SVC-11</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J144" s="7" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>ERP-025</t>
+          <t>ERP-024</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>공정 관리</t>
+          <t>작업지시 관리</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
@@ -9259,22 +9259,22 @@
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>M-4-2 · M-9-3</t>
+          <t>M-9-2</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>W-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I145" s="7" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, SVC-11</t>
         </is>
       </c>
       <c r="J145" s="7" t="inlineStr">
         <is>
-          <t>erp_work_process</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
@@ -9304,12 +9304,12 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>ERP-030</t>
+          <t>ERP-025</t>
         </is>
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>외주 제조 관리</t>
+          <t>공정 관리</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
@@ -9319,22 +9319,22 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>M-10-4 · M-9-5 · M-9-6</t>
+          <t>M-4-2 · M-9-3</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-19</t>
         </is>
       </c>
       <c r="I146" s="7" t="inlineStr">
         <is>
-          <t>SVC-09, INT-01</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
-          <t>com_company</t>
+          <t>erp_work_process</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
@@ -9352,24 +9352,24 @@
       <c r="A147" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-040</t>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-039</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>품질</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>ERP-012</t>
+          <t>ERP-030</t>
         </is>
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>부적합 처리</t>
+          <t>외주 제조 관리</t>
         </is>
       </c>
       <c r="F147" s="7" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>M-10-3</t>
+          <t>M-10-4 · M-9-5 · M-9-6</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="I147" s="7" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, INT-01</t>
         </is>
       </c>
       <c r="J147" s="7" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
@@ -9412,7 +9412,7 @@
       <c r="A148" s="5" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>REQ-F-040</t>
         </is>
@@ -9424,12 +9424,12 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>ERP-027</t>
+          <t>ERP-012</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>품질 관리</t>
+          <t>부적합 처리</t>
         </is>
       </c>
       <c r="F148" s="7" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>M-10-1 · M-10-2</t>
+          <t>M-10-3</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -9472,24 +9472,24 @@
       <c r="A149" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-041</t>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-040</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>재무</t>
+          <t>품질</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>ERP-011</t>
+          <t>ERP-027</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>재무 프로세스</t>
+          <t>품질 관리</t>
         </is>
       </c>
       <c r="F149" s="7" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>M-12-1 · M-12-2 · M-12-3 · M-12-4</t>
+          <t>M-10-1 · M-10-2</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-042</t>
+          <t>REQ-F-041</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>Dashboard·마스터</t>
+          <t>재무</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>ERP-013</t>
+          <t>ERP-011</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>재무 프로세스</t>
         </is>
       </c>
       <c r="F150" s="7" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>M-14-3</t>
+          <t>M-12-1 · M-12-2 · M-12-3 · M-12-4</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
-          <t>com_company</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K150" s="5" t="inlineStr">
@@ -9592,7 +9592,7 @@
       <c r="A151" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>REQ-F-042</t>
         </is>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>ERP-014</t>
+          <t>ERP-013</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
@@ -9619,22 +9619,22 @@
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>M-14-4</t>
+          <t>M-14-3</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>W-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I151" s="7" t="inlineStr">
         <is>
-          <t>SVC-09, FE-01</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J151" s="7" t="inlineStr">
         <is>
-          <t>erp_process_event, cst_*</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>ERP-015</t>
+          <t>ERP-014</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>회사 마스터</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -9679,27 +9679,27 @@
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>M-14-2 · M-6-1</t>
+          <t>M-14-4</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-10</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr">
         <is>
-          <t>SVC-09</t>
+          <t>SVC-09, FE-01</t>
         </is>
       </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
-          <t>com_company</t>
+          <t>erp_process_event, cst_*</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L152" s="5" t="inlineStr">
@@ -9712,34 +9712,34 @@
       <c r="A153" s="5" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-043</t>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-042</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>AI 학습 파이프라인</t>
+          <t>Dashboard·마스터</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>ERP-015</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>도면 학습 파이프라인</t>
+          <t>회사 마스터</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
-          <t>AI AI 기능</t>
+          <t>ERP ERP 업무</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>M-0-1</t>
+          <t>M-14-2 · M-6-1</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -9749,17 +9749,17 @@
       </c>
       <c r="I153" s="7" t="inlineStr">
         <is>
-          <t>AI-02, FE-04</t>
+          <t>SVC-09</t>
         </is>
       </c>
       <c r="J153" s="7" t="inlineStr">
         <is>
-          <t>(RAG 인덱스)</t>
+          <t>com_company</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L153" s="5" t="inlineStr">
@@ -9772,7 +9772,7 @@
       <c r="A154" s="5" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="B154" s="6" t="inlineStr">
         <is>
           <t>REQ-F-043</t>
         </is>
@@ -9784,12 +9784,12 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>메타데이터 추출</t>
+          <t>도면 학습 파이프라인</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="I154" s="7" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>AI-02, FE-04</t>
         </is>
       </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>(RAG 인덱스)</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>2D 엔티티 파싱·OCR</t>
+          <t>메타데이터 추출</t>
         </is>
       </c>
       <c r="F155" s="7" t="inlineStr">
@@ -9892,24 +9892,24 @@
       <c r="A156" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-044</t>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-043</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>AI 생성</t>
+          <t>AI 학습 파이프라인</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>Macro 자동 생성</t>
+          <t>2D 엔티티 파싱·OCR</t>
         </is>
       </c>
       <c r="F156" s="7" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>M-0-2</t>
+          <t>M-0-1</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -9929,17 +9929,17 @@
       </c>
       <c r="I156" s="7" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L156" s="5" t="inlineStr">
@@ -9952,7 +9952,7 @@
       <c r="A157" s="5" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>REQ-F-044</t>
         </is>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>4-Way 상호 변환</t>
+          <t>Macro 자동 생성</t>
         </is>
       </c>
       <c r="F157" s="7" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>UI 자동 제안</t>
+          <t>4-Way 상호 변환</t>
         </is>
       </c>
       <c r="F158" s="7" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="I158" s="7" t="inlineStr">
         <is>
-          <t>AI-04</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
@@ -10072,24 +10072,24 @@
       <c r="A159" s="5" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-045</t>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-044</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>AI 생성</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>UI 자동 제안</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>M-1-8</t>
+          <t>M-0-2</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -10109,17 +10109,17 @@
       </c>
       <c r="I159" s="7" t="inlineStr">
         <is>
-          <t>AI-05</t>
+          <t>AI-04</t>
         </is>
       </c>
       <c r="J159" s="7" t="inlineStr">
         <is>
-          <t>(RAG 인덱스)</t>
+          <t>tbx_ui_form</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
@@ -10134,22 +10134,22 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-046</t>
+          <t>REQ-F-045</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>AI 승인 게이트</t>
+          <t>사내 자료 챗봇</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>AI-008</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>AI 생성물 승인 게이트</t>
+          <t>사내 자료 챗봇</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-1-8</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
@@ -10169,17 +10169,17 @@
       </c>
       <c r="I160" s="7" t="inlineStr">
         <is>
-          <t>SVC-10</t>
+          <t>AI-05</t>
         </is>
       </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
-          <t>sys_approval_request</t>
+          <t>(RAG 인덱스)</t>
         </is>
       </c>
       <c r="K160" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L160" s="5" t="inlineStr">
@@ -10194,52 +10194,52 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>REQ-F-047</t>
+          <t>REQ-F-046</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>모바일 기본</t>
+          <t>AI 승인 게이트</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>APP-001</t>
+          <t>AI-008</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>QR 정보 열람</t>
+          <t>AI 생성물 승인 게이트</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>APP 모바일 App</t>
+          <t>AI AI 기능</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>M-16-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>W-16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="7" t="inlineStr">
         <is>
-          <t>FE-05, INT-05</t>
+          <t>SVC-10</t>
         </is>
       </c>
       <c r="J161" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_approval_request</t>
         </is>
       </c>
       <c r="K161" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="L161" s="5" t="inlineStr">
@@ -10252,7 +10252,7 @@
       <c r="A162" s="5" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="5" t="inlineStr">
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>REQ-F-047</t>
         </is>
@@ -10264,12 +10264,12 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>APP-002</t>
+          <t>APP-001</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>모바일 승인</t>
+          <t>QR 정보 열람</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>M-16-2</t>
+          <t>M-16-1</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="I162" s="7" t="inlineStr">
         <is>
-          <t>FE-05, SVC-10</t>
+          <t>FE-05, INT-05</t>
         </is>
       </c>
       <c r="J162" s="7" t="inlineStr">
         <is>
-          <t>sys_approval_request</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="5" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>APP-003</t>
+          <t>APP-002</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>Project 소통</t>
+          <t>모바일 승인</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
@@ -10339,22 +10339,22 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>M-16-3</t>
+          <t>M-16-2</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-16</t>
         </is>
       </c>
       <c r="I163" s="7" t="inlineStr">
         <is>
-          <t>FE-05, SVC-13</t>
+          <t>FE-05, SVC-10</t>
         </is>
       </c>
       <c r="J163" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_approval_request</t>
         </is>
       </c>
       <c r="K163" s="5" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>APP-007</t>
+          <t>APP-003</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>공지·푸시</t>
+          <t>Project 소통</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>M-16-7</t>
+          <t>M-16-3</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="J164" s="7" t="inlineStr">
         <is>
-          <t>sys_notification</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="5" t="inlineStr">
@@ -10432,24 +10432,24 @@
       <c r="A165" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-048</t>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-047</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>현장 업무</t>
+          <t>모바일 기본</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>APP-004</t>
+          <t>APP-007</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>자재 입출고</t>
+          <t>공지·푸시</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>M-16-4</t>
+          <t>M-16-7</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="I165" s="7" t="inlineStr">
         <is>
-          <t>FE-05, SVC-09</t>
+          <t>FE-05, SVC-13</t>
         </is>
       </c>
       <c r="J165" s="7" t="inlineStr">
         <is>
-          <t>erp_process_event</t>
+          <t>sys_notification</t>
         </is>
       </c>
       <c r="K165" s="5" t="inlineStr">
@@ -10492,7 +10492,7 @@
       <c r="A166" s="5" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="5" t="inlineStr">
+      <c r="B166" s="6" t="inlineStr">
         <is>
           <t>REQ-F-048</t>
         </is>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>APP-005</t>
+          <t>APP-004</t>
         </is>
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>검수</t>
+          <t>자재 입출고</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>M-16-5</t>
+          <t>M-16-4</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>APP-006</t>
+          <t>APP-005</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t>유지보수</t>
+          <t>검수</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>M-11-2 · M-16-6</t>
+          <t>M-16-5</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>APP-008</t>
+          <t>APP-006</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>AR 뷰</t>
+          <t>유지보수</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>M-16-8</t>
+          <t>M-11-2 · M-16-6</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="I168" s="7" t="inlineStr">
         <is>
-          <t>FE-05, INT-02</t>
+          <t>FE-05, SVC-09</t>
         </is>
       </c>
       <c r="J168" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>erp_process_event</t>
         </is>
       </c>
       <c r="K168" s="5" t="inlineStr">
@@ -10672,34 +10672,34 @@
       <c r="A169" s="5" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-049</t>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-048</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>관리 콘솔</t>
+          <t>현장 업무</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>ADM-001</t>
+          <t>APP-008</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>테넌트 관리</t>
+          <t>AR 뷰</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>ADM 관리 콘솔</t>
+          <t>APP 모바일 App</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M-16-8</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -10709,17 +10709,17 @@
       </c>
       <c r="I169" s="7" t="inlineStr">
         <is>
-          <t>FE-04</t>
+          <t>FE-05, INT-02</t>
         </is>
       </c>
       <c r="J169" s="7" t="inlineStr">
         <is>
-          <t>sys_tenant</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L169" s="5" t="inlineStr">
@@ -10732,7 +10732,7 @@
       <c r="A170" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="5" t="inlineStr">
+      <c r="B170" s="6" t="inlineStr">
         <is>
           <t>REQ-F-049</t>
         </is>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>ADM-002</t>
+          <t>ADM-001</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>사용자·권한 관리 UI</t>
+          <t>테넌트 관리</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
@@ -10769,17 +10769,17 @@
       </c>
       <c r="I170" s="7" t="inlineStr">
         <is>
-          <t>FE-04, SVC-01</t>
+          <t>FE-04</t>
         </is>
       </c>
       <c r="J170" s="7" t="inlineStr">
         <is>
-          <t>sys_*</t>
+          <t>sys_tenant</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>ADM-003</t>
+          <t>ADM-002</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>승인 관리</t>
+          <t>사용자·권한 관리 UI</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
@@ -10829,17 +10829,17 @@
       </c>
       <c r="I171" s="7" t="inlineStr">
         <is>
-          <t>FE-04, SVC-10</t>
+          <t>FE-04, SVC-01</t>
         </is>
       </c>
       <c r="J171" s="7" t="inlineStr">
         <is>
-          <t>sys_approval_request</t>
+          <t>sys_*</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>ADM-004</t>
+          <t>ADM-003</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
-          <t>AI 학습 관리</t>
+          <t>승인 관리</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
@@ -10889,17 +10889,17 @@
       </c>
       <c r="I172" s="7" t="inlineStr">
         <is>
-          <t>FE-04, AI-02</t>
+          <t>FE-04, SVC-10</t>
         </is>
       </c>
       <c r="J172" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sys_approval_request</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>ADM-005</t>
+          <t>ADM-004</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>감사·사용량</t>
+          <t>AI 학습 관리</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
@@ -10949,17 +10949,17 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>FE-04, INF-07</t>
+          <t>FE-04, AI-02</t>
         </is>
       </c>
       <c r="J173" s="7" t="inlineStr">
         <is>
-          <t>sys_history</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="L173" s="5" t="inlineStr">
@@ -10972,54 +10972,54 @@
       <c r="A174" s="5" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>REQ-F-050</t>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-049</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>Duct 자동 설계</t>
+          <t>관리 콘솔</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>DUCT-001</t>
+          <t>ADM-005</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr">
         <is>
-          <t>건축도면 학습</t>
+          <t>감사·사용량</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>DUCT 건축 설비 설계</t>
+          <t>ADM 관리 콘솔</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>M-4-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>W-15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I174" s="7" t="inlineStr">
         <is>
-          <t>AI-02</t>
+          <t>FE-04, INF-07</t>
         </is>
       </c>
       <c r="J174" s="7" t="inlineStr">
         <is>
-          <t>(RAG 인덱스)</t>
+          <t>sys_history</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="L174" s="5" t="inlineStr">
@@ -11032,7 +11032,7 @@
       <c r="A175" s="5" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>REQ-F-050</t>
         </is>
@@ -11044,12 +11044,12 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>DUCT-002</t>
+          <t>DUCT-001</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>건축 도면 호출</t>
+          <t>건축도면 학습</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="I175" s="7" t="inlineStr">
         <is>
-          <t>SVC-04</t>
+          <t>AI-02</t>
         </is>
       </c>
       <c r="J175" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>(RAG 인덱스)</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>DUCT-003</t>
+          <t>DUCT-002</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>Duct 자재 DB</t>
+          <t>건축 도면 호출</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="I176" s="7" t="inlineStr">
         <is>
-          <t>SVC-05</t>
+          <t>SVC-04</t>
         </is>
       </c>
       <c r="J176" s="7" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>DUCT-004</t>
+          <t>DUCT-003</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>설비 설계 조건 설정</t>
+          <t>Duct 자재 DB</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="I177" s="7" t="inlineStr">
         <is>
-          <t>FE-01, ENG-01</t>
+          <t>SVC-05</t>
         </is>
       </c>
       <c r="J177" s="7" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>DUCT-005</t>
+          <t>DUCT-004</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>Duct 자동 배치</t>
+          <t>설비 설계 조건 설정</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="I178" s="7" t="inlineStr">
         <is>
-          <t>ENG-03</t>
+          <t>FE-01, ENG-01</t>
         </is>
       </c>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>dwg_document</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="K178" s="5" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>DUCT-006</t>
+          <t>DUCT-005</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>설비 기술자료 계산</t>
+          <t>Duct 자동 배치</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>ENG-01</t>
+          <t>ENG-03</t>
         </is>
       </c>
       <c r="J179" s="7" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>dwg_document</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
@@ -11344,52 +11344,112 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
+          <t>DUCT-006</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>설비 기술자료 계산</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>DUCT 건축 설비 설계</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>M-4-3</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>W-15</t>
+        </is>
+      </c>
+      <c r="I180" s="7" t="inlineStr">
+        <is>
+          <t>ENG-01</t>
+        </is>
+      </c>
+      <c r="J180" s="7" t="inlineStr">
+        <is>
+          <t>tbx_macro</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>REQ-F-050</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>Duct 자동 설계</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
           <t>DUCT-007</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr">
+      <c r="E181" s="7" t="inlineStr">
         <is>
           <t>설비-EDIM 연결</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>DUCT 건축 설비 설계</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>M-4-3</t>
         </is>
       </c>
-      <c r="H180" s="5" t="inlineStr">
+      <c r="H181" s="5" t="inlineStr">
         <is>
           <t>W-15</t>
         </is>
       </c>
-      <c r="I180" s="7" t="inlineStr">
+      <c r="I181" s="7" t="inlineStr">
         <is>
           <t>ENG-02</t>
         </is>
       </c>
-      <c r="J180" s="7" t="inlineStr">
+      <c r="J181" s="7" t="inlineStr">
         <is>
           <t>cpq_*</t>
         </is>
       </c>
-      <c r="K180" s="5" t="inlineStr">
+      <c r="K181" s="5" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="L180" s="5" t="inlineStr">
+      <c r="L181" s="5" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L180"/>
+  <autoFilter ref="A1:L181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C9"/>
+  <dimension ref="B2:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>v0.1 (자동 생성)</t>
+          <t>v0.2 (자동 생성)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-07 (v0.2 갱신 2026-07-15)</t>
         </is>
       </c>
     </row>
@@ -537,22 +537,34 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>추적 행</t>
+          <t>추적 범위</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>180건 (요구사항 50 × 기능 매핑)</t>
+          <t>본 RTM 은 요구사항(REQ-F/NFR) 중심 추적만 담당한다. 요구사항 확정 이후의 구현 증분(B/C/D/E/F/G 배치)은 docs/EDIM_미구현기능목록.md 가 배치 단위(구현·검증·버전)로 추적하며 RTM 형식을 확장하지 않는다 (C13 규칙, 2026-07-15 명문화).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>추적 행</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>180건 (요구사항 50 × 기능 매핑)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>커버리지</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>기능 179/179 연결 · 미연결 0건 · 해석불가 0건 (커버리지 시트 참조)</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_요구사항추적표.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +50,16 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A1A40"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +118,10 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11472,45 +11489,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>대상</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>내용</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>연결 고리</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>기재</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>판정 근거·주의</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>전 기능이 요구사항에 연결됨 (100%)</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>요구사항 → 기능 ID</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>180/180</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>이 고리만 100% 다. 종전 커버리지 시트의 '전 기능이 요구사항에 연결됨(100%)' 은 이 고리를 말한 것이며, 아래 고리들에는 해당하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>기능 → 메뉴 ID</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>154/180</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>미기재는 Phase4~5 항목이 다수</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>기능 → 화면 ID</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>100/180</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>기재된 것도 구현 화면코드와 체계가 다르다 — 아래 '식별자 체계' 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>기능 → 주 DB</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>162/180</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>참조 189건 중 실 테이블명이 아닌 표기 0건(와일드카드·설명 문구 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>식별자 체계 (2026-07-26 실측)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>화면 ID</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>4/103 일치</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>추적표는 W-01 계열, 구현(menus.ts)은 C-1·D-1·AI-08 계열을 쓴다. 일치하지 않는 것 99건. **없는 화면이 아니라 다른 이름**일 가능성이 크므로 추측으로 잇지 않았다 — 매핑은 사람이 정할 결정 사항이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>주 DB</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>189/189 실 테이블</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>실 스키마 107 테이블과 대조. 남은 것은 code_*·sys_* 같은 와일드카드와 '(RAG 인덱스)' 류 설명 문구, 그리고 컬럼 참조(cpq_run.dimension_values) 1건.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>열지 못한 것</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>REQ→기능→메뉴→화면→컴포넌트→DB 사슬은 앞 두 고리까지는 따라갈 수 있으나, 화면 이후는 식별자 체계가 달라 **코드로 이어지지 않는다**. 이 사슬을 실제 추적에 쓰려면 체계 통일 또는 매핑표 확정이 필요하다(Launch 차단 - 협의 항목).</t>
         </is>
       </c>
     </row>
